--- a/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:29</t>
+          <t>2026-09-01 03:15:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:30</t>
+          <t>2026-09-01 03:15:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:31</t>
+          <t>2026-09-01 03:15:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:08:33</t>
+          <t>2026-09-01 03:15:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.71%545</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.71%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>545</v>
+        <v>568</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.40%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.9%819</t>
+          <t>+6.72%874</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3530</v>
+        <v>3425</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:11</t>
+          <t>2026-09-01 15:28:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5990</v>
+        <v>5885</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,17 +1424,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0%742</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>731</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-1.85%2125</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.33%496.5</t>
+          <t>+1.31%503</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>496.5</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.37%136</t>
+          <t>0%136</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.81%257</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>279</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:13</t>
+          <t>2026-09-01 15:28:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.66%76.2</t>
+          <t>0%76.2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.4%1060</t>
+          <t>+3.77%1100</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+3.77%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2367,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.52%999</t>
+          <t>+1.1%1010</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2428,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2489,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.14%721</t>
+          <t>+3.19%744</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.8%338.5</t>
+          <t>+1.03%342</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>338.5</v>
+        <v>342</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.11%248.5</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>248.5</v>
+        <v>252</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.19%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.86%233.5</t>
+          <t>+1.93%238</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>233.5</v>
+        <v>238</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.73%41.35</t>
+          <t>+1.45%41.95</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>41.35</v>
+        <v>41.95</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%144</t>
+          <t>+0.69%145</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+4.74%110.5</t>
+          <t>+0.45%111</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+4.74%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110.5</v>
+        <v>111</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.36%33.85</t>
+          <t>+3.25%34.95</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>33.85</v>
+        <v>34.95</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.58%39.75</t>
+          <t>+0.38%39.9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>39.75</v>
+        <v>39.9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:14</t>
+          <t>2026-09-01 15:28:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.19%65.4</t>
+          <t>+1.99%66.7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.73%48.55</t>
+          <t>-0.1%48.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.8%38.55</t>
+          <t>+4.54%40.3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+4.54%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+3.27%41.1</t>
+          <t>+0.97%41.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+3.27%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.47%64.7</t>
+          <t>+2.78%66.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.92%216.5</t>
+          <t>-0.23%216</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:15</t>
+          <t>2026-09-01 15:28:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.98%151.5</t>
+          <t>+1.32%153.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:28</t>
+          <t>2026-09-01 15:55:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:29</t>
+          <t>2026-09-01 15:55:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:31</t>
+          <t>2026-09-01 15:55:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:32</t>
+          <t>2026-09-01 15:55:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.27%1,380,000</t>
+          <t>9.39%1,380,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.39%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.18%13,800,000</t>
+          <t>8.63%13,800,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>8.63%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.68%500,000</t>
+          <t>8.54%500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.68%</t>
+          <t>8.54%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.12%5,000,000</t>
+          <t>5.86%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>5.86%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6669緯穎科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3410</v>
+        <v>7800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.24%1,250,000</t>
+          <t>5.46%580,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1250000</v>
+        <v>580000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7800</v>
+        <v>3410</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.04%580,000</t>
+          <t>5.14%1,250,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>5.14%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>580000</v>
+        <v>1250000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.01%7,500,000</t>
+          <t>5.14%7,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.14%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.90%3,250,000</t>
+          <t>4.80%3,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.80%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.33%900,000</t>
+          <t>4.69%900,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.11%4,100,000</t>
+          <t>4.32%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.99%1,600,000</t>
+          <t>4.26%1,600,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.89%900,000</t>
+          <t>3.72%900,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.52%2,000,000</t>
+          <t>3.50%2,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:19</t>
+          <t>2026-09-01 17:52:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,25 +1358,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3653健策精密</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5885</v>
+        <v>17120</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.49%340,000</t>
+          <t>2.49%120,500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1385,11 +1385,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>340000</v>
+        <v>120500</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,40 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.48%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
+          <t>+5.46%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5410</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.45%2,700,000</t>
+          <t>2.48%380,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2700000</v>
+        <v>380000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,40 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3653健策精密</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+5.46%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>5410</t>
-        </is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>5885</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.39%380,000</t>
+          <t>2.41%340,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>380000</v>
+        <v>340000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,40 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>3026禾伸堂企</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.57%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
+          <t>-1.48%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>731</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.37%120,500</t>
+          <t>2.38%2,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>120500</v>
+        <v>2700000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1621,19 +1615,17 @@
           <t>-1.85%</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2125</t>
-        </is>
+      <c r="H20" t="n">
+        <v>2125</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33%880,000</t>
+          <t>2.26%880,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1684,19 +1676,17 @@
           <t>+0.17%</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>5870</t>
-        </is>
+      <c r="H21" t="n">
+        <v>5870</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.15%300,000</t>
+          <t>2.13%300,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1734,40 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3711日月光投</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.45%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>7580</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>3711日月光投</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.92%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>7580</t>
-        </is>
+          <t>+4.45%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>610</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,36 +1846,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.31%503</t>
+          <t>+1.03%342</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.31%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
+          <t>+1.03%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>342</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1910,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,36 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2317鴻海精密</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+6.68%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2315</t>
-        </is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>256</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1973,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,36 +1968,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.25%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+          <t>+6.68%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2315</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2036,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,36 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>+1.93%238</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>238</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2099,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,32 +2090,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%136</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+          <t>+3.57%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2030</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2162,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,36 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2308台達電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+8.56%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1865</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1450</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2225,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:21</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,36 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%76.2</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>76.2</t>
-        </is>
+          <t>+2.25%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>182</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2288,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2297,38 +2269,38 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2404漢唐集成</t>
+          <t>5347世界先進</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>+1.32%153.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1100</v>
+        <v>153.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2349,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>2881富邦金融</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.1%1010</t>
+          <t>+0.69%145</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1010</v>
+        <v>145</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2410,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2030</v>
+        <v>132.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2471,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,30 +2456,30 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2379瑞昱半導</t>
+          <t>2357華碩電腦</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.19%744</t>
+          <t>+1.1%1010</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>744</v>
+        <v>1010</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2532,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,30 +2517,30 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>2882國泰金融</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.03%342</t>
+          <t>+0.45%111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2593,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,30 +2578,30 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2308台達電子</t>
+          <t>2379瑞昱半導</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>+3.19%744</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>+3.19%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1865</v>
+        <v>744</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2654,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2313華通電腦</t>
+          <t>2885元大金融</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.41%252</t>
+          <t>+1.99%66.7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>252</v>
+        <v>66.7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0%1,253</t>
+          <t>&lt;0.01%9,360</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1253</v>
+        <v>9360</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2715,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,30 +2700,30 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2317鴻海精密</t>
+          <t>2891中國信託</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.4%256</t>
+          <t>+2.78%66.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>256</v>
+        <v>66.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2776,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.93%238</t>
+          <t>+1.31%503</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>238</v>
+        <v>503</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2837,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.45%41.95</t>
+          <t>-0.1%48.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>41.95</v>
+        <v>48.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2898,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,21 +2883,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2881富邦金融</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.69%145</t>
+          <t>+4.54%40.3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+4.54%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>145</v>
+        <v>40.3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,21 +2944,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.45%111</t>
+          <t>+0.97%41.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>111</v>
+        <v>41.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.25%34.95</t>
+          <t>+1.45%41.95</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>34.95</v>
+        <v>41.95</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3060,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3081,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.38%39.9</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>39.9</v>
+        <v>279</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3121,7 +3093,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3142,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:22</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3155,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2885元大金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.99%66.7</t>
+          <t>+0.38%39.9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>66.7</v>
+        <v>39.9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0%9,360</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3182,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9360</v>
+        <v>9000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3203,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:37</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3212,27 +3184,25 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.1%48.5</t>
+          <t>+3.25%34.95</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
+          <t>+3.25%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>34.95</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3266,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3279,27 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2313華通電腦</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.54%40.3</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.54%</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+          <t>+1.41%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>252</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,253</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3308,7 +3276,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>1253</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3329,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3342,27 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2912統一超商</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.97%41.5</t>
+          <t>-0.23%216</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.97%</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>216</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3371,7 +3337,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3392,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3405,27 +3371,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2891中國信託</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+2.78%66.5</t>
+          <t>0%196</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+2.78%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>196</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3434,7 +3398,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3455,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3468,23 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2912統一超商</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.23%216</t>
+          <t>0%136</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>136</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3518,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:23</t>
+          <t>2026-09-01 17:52:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3531,27 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5347世界先進</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>0%76.2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.32%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>153.5</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>76.2</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3560,7 +3520,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:34</t>
+          <t>2026-09-01 20:33:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:35</t>
+          <t>2026-09-01 20:33:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:37</t>
+          <t>2026-09-01 20:33:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:38</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:38</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:38</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:38</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:38</t>
+          <t>2026-09-01 20:33:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
